--- a/InputData/bldgs/CL/Component Lifetime.xlsx
+++ b/InputData/bldgs/CL/Component Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\bldgs\CL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\CL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CF370-788E-4784-B578-F159A2380095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53986B37-0C23-4882-900B-998E1BC0DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="commercial" sheetId="9" r:id="rId3"/>
     <sheet name="lighting" sheetId="3" r:id="rId4"/>
     <sheet name="other components" sheetId="6" r:id="rId5"/>
-    <sheet name="CL" sheetId="8" r:id="rId6"/>
+    <sheet name="Data Centers" sheetId="10" r:id="rId6"/>
+    <sheet name="CL" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="123">
   <si>
     <t>Lifetime (years)</t>
   </si>
@@ -376,6 +379,36 @@
   </si>
   <si>
     <t>Age at which reaches 95% retirement</t>
+  </si>
+  <si>
+    <t>Data center assumptions</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. Their cooling, ventilation and power-distribution equipment uses the commercial lifetimes; their IT load (the 'other component' end use) uses the IT equipment lifetime below.</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>Lifetime of data-center IT equipment (years)</t>
+  </si>
+  <si>
+    <t>Servers and network equipment are typically replaced on a 3-6 year refresh cycle; 5 years is used here. This sets the lifetime of the 'other component' end use for data centers.</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers use the commercial lifetimes except for IT equipment ('other component'), which uses the lifetime on the 'Data Centers' tab.</t>
   </si>
 </sst>
 </file>
@@ -495,7 +528,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -542,6 +575,12 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -898,19 +937,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.54296875" customWidth="1"/>
-    <col min="5" max="5" width="9.1328125" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>57</v>
       </c>
@@ -918,156 +957,164 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>2000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="59" x14ac:dyDescent="0.75">
+    <row r="26" spans="2:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B26" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +1130,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.86328125" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="55.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1097,7 +1144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1105,7 +1152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1113,7 +1160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1137,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1145,7 +1192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1161,7 +1208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1169,7 +1216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -1178,7 +1225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -1186,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1194,7 +1241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1202,7 +1249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1210,7 +1257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1218,7 +1265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1226,7 +1273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1234,7 +1281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>10</v>
       </c>
@@ -1243,7 +1290,7 @@
         <v>15.833333333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>71</v>
       </c>
@@ -1251,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -1262,7 +1309,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1274,7 +1321,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>10</v>
       </c>
@@ -1283,7 +1330,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -1291,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1299,7 +1346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1307,7 +1354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1315,7 +1362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1323,7 +1370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1331,7 +1378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1339,7 +1386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1347,7 +1394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1355,7 +1402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1363,7 +1410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1371,7 +1418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1379,7 +1426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1387,7 +1434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1395,7 +1442,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -1403,7 +1450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -1411,7 +1458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
@@ -1428,17 +1475,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A23E7D3-3248-4A9A-AC48-726EA7E84B1F}">
   <dimension ref="A1:AC58"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="H6" t="s">
         <v>97</v>
       </c>
@@ -1483,7 +1530,7 @@
         <v>Other</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="H7" s="1" t="s">
         <v>108</v>
       </c>
@@ -1551,7 +1598,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="H8" s="1" t="s">
         <v>110</v>
       </c>
@@ -1619,7 +1666,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="D9" s="20" t="s">
         <v>112</v>
       </c>
@@ -1715,7 +1762,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -1821,7 +1868,7 @@
         <v>0.16814591125816214</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -1927,7 +1974,7 @@
         <v>0.29850854713832564</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>105</v>
       </c>
@@ -2033,7 +2080,7 @@
         <v>0.40144099339352235</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>106</v>
       </c>
@@ -2139,7 +2186,7 @@
         <v>0.48401045051364899</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -2245,7 +2292,7 @@
         <v>0.55116744827256792</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -2351,7 +2398,7 @@
         <v>0.60645889186864177</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -2457,7 +2504,7 @@
         <v>0.6524769751358459</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -2563,7 +2610,7 @@
         <v>0.6911498078401257</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
@@ -2669,7 +2716,7 @@
         <v>0.72393427629614004</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -2775,7 +2822,7 @@
         <v>0.75194687652894188</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -2881,7 +2928,7 @@
         <v>0.77605424063132289</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G21">
         <v>60</v>
       </c>
@@ -2974,7 +3021,7 @@
         <v>0.79693690091094105</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D22" s="21">
         <f>AVERAGE(D10:D20)</f>
         <v>176.36363636363637</v>
@@ -3071,7 +3118,7 @@
         <v>0.81513493579056595</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G23">
         <v>70</v>
       </c>
@@ -3164,7 +3211,7 @@
         <v>0.83108113075017753</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G24">
         <v>75</v>
       </c>
@@ -3257,7 +3304,7 @@
         <v>0.84512539621074256</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G25">
         <v>80</v>
       </c>
@@ -3350,7 +3397,7 @@
         <v>0.85755297159742183</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G26">
         <v>85</v>
       </c>
@@ -3443,7 +3490,7 @@
         <v>0.86859815270338192</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G27">
         <v>90</v>
       </c>
@@ -3536,7 +3583,7 @@
         <v>0.87845475313082022</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G28">
         <v>95</v>
       </c>
@@ -3629,7 +3676,7 @@
         <v>0.88728415527989801</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G29">
         <v>100</v>
       </c>
@@ -3722,7 +3769,7 @@
         <v>0.89522156298373423</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G30">
         <v>105</v>
       </c>
@@ -3815,7 +3862,7 @@
         <v>0.90238089891375506</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G31">
         <v>110</v>
       </c>
@@ -3908,7 +3955,7 @@
         <v>0.90885867107417728</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G32">
         <v>115</v>
       </c>
@@ -4001,7 +4048,7 @@
         <v>0.91473704818530821</v>
       </c>
     </row>
-    <row r="33" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="33" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G33">
         <v>120</v>
       </c>
@@ -4094,7 +4141,7 @@
         <v>0.92008632296390402</v>
       </c>
     </row>
-    <row r="34" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="34" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G34">
         <v>125</v>
       </c>
@@ -4187,7 +4234,7 @@
         <v>0.924966898131519</v>
       </c>
     </row>
-    <row r="35" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="35" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G35">
         <v>130</v>
       </c>
@@ -4280,7 +4327,7 @@
         <v>0.92943089756628083</v>
       </c>
     </row>
-    <row r="36" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="36" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G36">
         <v>135</v>
       </c>
@@ -4373,7 +4420,7 @@
         <v>0.93352348101112881</v>
       </c>
     </row>
-    <row r="37" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="37" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G37">
         <v>140</v>
       </c>
@@ -4466,7 +4513,7 @@
         <v>0.93728392282576456</v>
       </c>
     </row>
-    <row r="38" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="38" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G38">
         <v>145</v>
       </c>
@@ -4559,7 +4606,7 @@
         <v>0.94074650177321439</v>
       </c>
     </row>
-    <row r="39" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="39" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G39">
         <v>150</v>
       </c>
@@ -4652,7 +4699,7 @@
         <v>0.9439412385924304</v>
       </c>
     </row>
-    <row r="40" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="40" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G40">
         <v>155</v>
       </c>
@@ -4745,7 +4792,7 @@
         <v>0.94689451028330174</v>
       </c>
     </row>
-    <row r="41" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="41" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G41">
         <v>160</v>
       </c>
@@ -4838,7 +4885,7 @@
         <v>0.94962956400924592</v>
       </c>
     </row>
-    <row r="42" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="42" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G42">
         <v>165</v>
       </c>
@@ -4931,7 +4978,7 @@
         <v>0.95216694885900344</v>
       </c>
     </row>
-    <row r="43" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="43" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G43">
         <v>170</v>
       </c>
@@ -5024,7 +5071,7 @@
         <v>0.95452488007474379</v>
       </c>
     </row>
-    <row r="44" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="44" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G44">
         <v>175</v>
       </c>
@@ -5117,7 +5164,7 @@
         <v>0.95671954750423149</v>
       </c>
     </row>
-    <row r="45" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="45" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G45">
         <v>180</v>
       </c>
@@ -5210,7 +5257,7 @@
         <v>0.95876537778834703</v>
       </c>
     </row>
-    <row r="46" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="46" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G46">
         <v>185</v>
       </c>
@@ -5303,7 +5350,7 @@
         <v>0.96067525801457798</v>
       </c>
     </row>
-    <row r="47" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="47" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G47">
         <v>190</v>
       </c>
@@ -5396,7 +5443,7 @@
         <v>0.96246072714833442</v>
       </c>
     </row>
-    <row r="48" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="48" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G48">
         <v>195</v>
       </c>
@@ -5489,7 +5536,7 @@
         <v>0.96413214041796713</v>
       </c>
     </row>
-    <row r="49" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="49" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G49">
         <v>200</v>
       </c>
@@ -5582,7 +5629,7 @@
         <v>0.96569881091551146</v>
       </c>
     </row>
-    <row r="50" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="50" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G50">
         <v>205</v>
       </c>
@@ -5675,7 +5722,7 @@
         <v>0.96716913193669363</v>
       </c>
     </row>
-    <row r="51" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="51" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G51">
         <v>210</v>
       </c>
@@ -5768,7 +5815,7 @@
         <v>0.96855068298436331</v>
       </c>
     </row>
-    <row r="52" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="52" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G52">
         <v>215</v>
       </c>
@@ -5861,7 +5908,7 @@
         <v>0.96985032187103903</v>
       </c>
     </row>
-    <row r="53" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="53" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G53">
         <v>220</v>
       </c>
@@ -5954,7 +6001,7 @@
         <v>0.97107426495654525</v>
       </c>
     </row>
-    <row r="54" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="54" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G54">
         <v>225</v>
       </c>
@@ -6047,7 +6094,7 @@
         <v>0.97222815722839884</v>
       </c>
     </row>
-    <row r="55" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="55" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G55">
         <v>230</v>
       </c>
@@ -6140,7 +6187,7 @@
         <v>0.97331713366192141</v>
       </c>
     </row>
-    <row r="56" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="56" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G56">
         <v>235</v>
       </c>
@@ -6233,7 +6280,7 @@
         <v>0.9743458730730904</v>
       </c>
     </row>
-    <row r="57" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="57" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G57">
         <v>240</v>
       </c>
@@ -6326,7 +6373,7 @@
         <v>0.97531864549119962</v>
       </c>
     </row>
-    <row r="58" spans="7:29" x14ac:dyDescent="0.75">
+    <row r="58" spans="7:29" x14ac:dyDescent="0.25">
       <c r="G58">
         <v>245</v>
       </c>
@@ -6429,23 +6476,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.1328125" customWidth="1"/>
-    <col min="2" max="2" width="21.40625" customWidth="1"/>
-    <col min="3" max="3" width="22.86328125" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -6459,7 +6506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -6474,32 +6521,32 @@
         <v>9.1324200913242013</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -6512,19 +6559,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1328125" customWidth="1"/>
-    <col min="2" max="2" width="33.40625" customWidth="1"/>
-    <col min="3" max="3" width="20.40625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
@@ -6535,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1000</v>
       </c>
@@ -6546,7 +6593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1000</v>
       </c>
@@ -6557,7 +6604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1000</v>
       </c>
@@ -6568,7 +6615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1000</v>
       </c>
@@ -6579,7 +6626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1000</v>
       </c>
@@ -6590,7 +6637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="12" t="s">
         <v>10</v>
@@ -6606,20 +6653,147 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684DFCE3-0442-4C95-A8F4-639865C18EE0}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.86328125" customWidth="1"/>
-    <col min="2" max="2" width="18.40625" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
@@ -6632,8 +6806,11 @@
       <c r="D1" s="14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -6649,8 +6826,12 @@
         <f>$B2</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E2" s="13">
+        <f>$D2</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -6666,8 +6847,12 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E3" s="13">
+        <f>$D3</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -6683,8 +6868,12 @@
         <f>ROUND('HUD Appendix C Data'!$B$24,0)</f>
         <v>176</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E4" s="13">
+        <f>$D4</f>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -6700,8 +6889,12 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E5" s="13">
+        <f>$D5</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -6717,8 +6910,12 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E6" s="13">
+        <f>$D6</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -6733,6 +6930,10 @@
       <c r="D7" s="13">
         <f t="shared" si="0"/>
         <v>15</v>
+      </c>
+      <c r="E7">
+        <f>'Data Centers'!$B$5</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
